--- a/docs/test/unit/NOUS-96/観点表_cloudflareClient.xlsx
+++ b/docs/test/unit/NOUS-96/観点表_cloudflareClient.xlsx
@@ -2781,7 +2781,7 @@
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>400・401 以外の 4xx（403・404・413）は ServerError で、再試行の対象になる</t>
+          <t>400・401・429 以外の 4xx（403・404・413）は ServerError で、再試行しない</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
@@ -2792,7 +2792,7 @@
       </c>
       <c r="H35" s="5" t="inlineStr">
         <is>
-          <t>ServerError、retryable 真（実装の値）</t>
+          <t>ServerError、retryable 偽（IF-001 の再試行の対象は timeout・429（3036 以外）・5xx に限られる）</t>
         </is>
       </c>
       <c r="I35" s="5" t="inlineStr">
@@ -2809,7 +2809,7 @@
       <c r="L35" s="5" t="inlineStr"/>
       <c r="M35" s="5" t="inlineStr">
         <is>
-          <t>TC-UT_LLM-037 400・401 以外の 4xx（403・404・413）は ServerError で、再試行の対象になる</t>
+          <t>TC-UT_LLM-037 400・401・429 以外の 4xx（403・404・413）は ServerError で、再試行しない</t>
         </is>
       </c>
       <c r="N35" s="6" t="inlineStr">
@@ -2822,7 +2822,8 @@
       <c r="Q35" s="7" t="inlineStr">
         <is>
           <t>既存テスト：なし（DEV-13 は 400・401・5xx だけ）
-設計書（generation 2章）は 400・401・429・5xx だけを定める。403 などの扱いは確認事項 1</t>
+疑い：ServerError.retryable が 400・401 以外を真にするため、403・404・413 も再試行の対象になる（疑い 1）
+期待結果は BE 詳細設計 generation 2章 IF-001 の再試行の欄（2026-10-23 Kouhei Tajima 判断）</t>
         </is>
       </c>
     </row>
@@ -4979,7 +4980,7 @@
       </c>
       <c r="B35" s="13" t="inlineStr">
         <is>
-          <t>400・401 以外の 4xx（403・404・413）は ServerError で、再試行の対象になる</t>
+          <t>400・401・429 以外の 4xx（403・404・413）は ServerError で、再試行しない</t>
         </is>
       </c>
       <c r="C35" s="13" t="inlineStr">
@@ -5917,14 +5918,14 @@
     <row r="40" ht="30" customHeight="1">
       <c r="A40" s="18" t="inlineStr">
         <is>
-          <t>・確認事項 1：toLlmError は 400・401・429 以外の 4xx（403 の権限不足、404 のモデル名の誤り、413 の本文が大きすぎるなど）を ServerError として再試行の対象にしている。設計書（generation 2章）は 400・401 を「入力や権限の問題で再試行しない」としているが、ほかの 4xx は記載がない。403・404 も繰り返して直るものではないため、再試行しない側に入れるべきかを確認したい。単体テストは実装の値（再試行する）を期待値にした（TC-UT_LLM-037）。</t>
+          <t>・疑い 1：toLlmError は 400・401・429 以外の 4xx（403 の権限不足、404 のモデル名の誤り、413 の本文が大きすぎるなど）を ServerError にし、ServerError.retryable が 400・401 以外を真にするため、再試行の対象になっている（llmClient.ts:86、cloudflareClient.ts:109-110）。設計書（generation 2章 IF-001）は再試行の対象を timeout・429（3036 以外）・5xx に限っているので、403・404・413 は再試行しないのが仕様（2026-10-23 Kouhei Tajima 判断）。TC-UT_LLM-037 は仕様どおり「再試行しない」を期待結果にしており、実施のときに NG になる見込み。</t>
         </is>
       </c>
     </row>
     <row r="41" ht="30" customHeight="1">
       <c r="A41" s="18" t="inlineStr">
         <is>
-          <t>・確認事項 2：buildRequestBody は、Gemma 4・GLM・Qwen3 以外のモデルでは思考を止める指定を何も送らない（TC-UT_LLM-029）。world_settings.model_id は DB の CHECK で Gemma 4 と Qwen3 の 2 つに限られるため、今は影響がない。モデルを足すときに見直す。</t>
+          <t>・確認事項 1：buildRequestBody は、Gemma 4・GLM・Qwen3 以外のモデルでは思考を止める指定を何も送らない（TC-UT_LLM-029）。world_settings.model_id は DB の CHECK で Gemma 4 と Qwen3 の 2 つに限られるため、今は影響がない。モデルを足すときに見直す。</t>
         </is>
       </c>
     </row>
